--- a/out/Attention-Mamba1_repeat_3_000001.xlsx
+++ b/out/Attention-Mamba1_repeat_3_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.6780933625747476</v>
+        <v>1.990389075499147</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.6780933625747476</v>
+        <v>1.990389075499147</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.278093362574747</v>
+        <v>2.590389075499147</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.278093362574747</v>
+        <v>2.590389075499147</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.278093362574747</v>
+        <v>2.590389075499147</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.278093362574747</v>
+        <v>2.590389075499147</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.278093362574747</v>
+        <v>2.590389075499147</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.278093362574747</v>
+        <v>2.590389075499147</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.278093362574747</v>
+        <v>2.590389075499147</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.6780933625747476</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.6780933625747476</v>
+        <v>1.990389075499147</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.6780933625747476</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.6780933625747476</v>
+        <v>1.990389075499147</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.6780933625747476</v>
+        <v>1.990389075499147</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.6780933625747476</v>
+        <v>2.590389075499147</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.6780933625747476</v>
+        <v>2.590389075499147</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.6780933625747476</v>
+        <v>2.590389075499147</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.6780933625747476</v>
+        <v>2.590389075499147</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.6780933625747476</v>
+        <v>2.590389075499147</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.6780933625747476</v>
+        <v>2.590389075499147</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.6780933625747476</v>
+        <v>2.590389075499147</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.6780933625747476</v>
+        <v>1.990389075499147</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.6780933625747476</v>
+        <v>1.990389075499147</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.6780933625747476</v>
+        <v>1.990389075499147</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.6780933625747476</v>
+        <v>1.990389075499147</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.6780933625747476</v>
+        <v>1.990389075499147</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.6780933625747476</v>
+        <v>1.990389075499147</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.6780933625747476</v>
+        <v>1.990389075499147</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.6780933625747476</v>
+        <v>1.990389075499147</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.6780933625747476</v>
+        <v>1.990389075499147</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.6780933625747476</v>
+        <v>1.990389075499147</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.6780933625747476</v>
+        <v>1.990389075499147</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.6780933625747476</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.6780933625747476</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.6780933625747476</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.6780933625747476</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.6780933625747476</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.6780933625747476</v>
+        <v>1.990389075499147</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.6780933625747476</v>
+        <v>2.590389075499147</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.6780933625747476</v>
+        <v>2.590389075499147</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.6780933625747476</v>
+        <v>2.590389075499147</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.6780933625747476</v>
+        <v>-0.5557497644722087</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0001553836047814693</v>
+        <v>-5.460887144110166e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.06690366882491081</v>
+        <v>0.02351288745798814</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.6780933625747476</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.133985885853162</v>
+        <v>0.04708873956686502</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2584842548940672</v>
+        <v>0.09084271911741791</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.6780933625747476</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.5842218166266187</v>
+        <v>0.20532286158494</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.07951069678184169</v>
+        <v>0.02794372963861532</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.6780933625747476</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.4844327552037521</v>
+        <v>0.170251964840618</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.01613351839373679</v>
+        <v>0.005668951760816302</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.6780933625747476</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4370636886960296</v>
+        <v>0.1536026492201853</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01397234394911369</v>
+        <v>0.00490778567348298</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.6780933625747476</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.4488570223789166</v>
+        <v>0.1577449706925822</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.006829273075512044</v>
+        <v>0.002396760823730598</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.6780933625747476</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.4485266902939701</v>
+        <v>0.1576256236653321</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.003256345633814244</v>
+        <v>0.001141582484659956</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.6780933625747476</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.4482035681335223</v>
+        <v>0.1575087935252511</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001353929605622277</v>
+        <v>0.0004726573542088954</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.6780933625747476</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.4476506684643822</v>
+        <v>0.1573112093728043</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0009364392178318687</v>
+        <v>0.0003260470692212063</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.6780933625747476</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.4481691592863425</v>
+        <v>0.157490213662504</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0003880150844352673</v>
+        <v>0.0001328774230641758</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.6780933625747476</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.4480075992920722</v>
+        <v>0.157430206541802</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.000198792341387696</v>
+        <v>6.649436238847041e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.6780933625747476</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.4480167832095169</v>
+        <v>0.1574301980631025</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>7.530420522688556e-05</v>
+        <v>2.334266066831255e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.4479676905145862</v>
+        <v>0.15740963593548</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>3.852012786152756e-05</v>
+        <v>1.0461098056069e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.6780933625747476</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.4479699102782724</v>
+        <v>0.1574071838605092</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>1.645752582315463e-05</v>
+        <v>2.340732518447637e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.4479642480169663</v>
+        <v>0.1574019520532899</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>5.123686696358992e-06</v>
+        <v>-1.270220690815108e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.447957981009678</v>
+        <v>0.157396497008007</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-3.882814673064221e-07</v>
+        <v>-3.616484440191926e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.4479515346964202</v>
+        <v>0.1573909913741797</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-2.932986608081494e-06</v>
+        <v>-4.173194643232597e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4479460509595846</v>
+        <v>0.1573857978794456</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.36427134277522e-06</v>
+        <v>-4.68213567138761e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.4479405707350173</v>
+        <v>0.1573806055937286</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.817481666896968e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4479351633923603</v>
+        <v>0.1573804700851228</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.777674021158921e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.278093362574747</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4479302422386389</v>
+        <v>0.1573805099405951</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.703898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4479302820941112</v>
+        <v>0.1573805497960674</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.278093362574747</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4479302741230167</v>
+        <v>0.157380541824973</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.703898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4479304335449059</v>
+        <v>0.1573807012468621</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.278093362574747</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4479303378917724</v>
+        <v>0.1573806055937286</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.278093362574747</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4479306886199287</v>
+        <v>0.1573809563218849</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.703898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4479304415160003</v>
+        <v>0.1573807092179565</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.278093362574747</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4479304016605281</v>
+        <v>0.1573806693624842</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4479303378917724</v>
+        <v>0.1573806055937286</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4479304096316225</v>
+        <v>0.1573806773335787</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.6780933625747476</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4479303378917724</v>
+        <v>0.1573806055937286</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.278093362574747</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4479304415160003</v>
+        <v>0.1573807092179565</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.278093362574747</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.447930537169134</v>
+        <v>0.1573808048710902</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.703898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4479304734003781</v>
+        <v>0.1573807411023344</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4479304335449059</v>
+        <v>0.1573807012468621</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.6780933625747476</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4479304096316225</v>
+        <v>0.1573806773335787</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4479301625276944</v>
+        <v>0.1573804302296506</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4479300828167496</v>
+        <v>0.1573803505187058</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.6780933625747476</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4479301306433163</v>
+        <v>0.1573803983452725</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4479302502097334</v>
+        <v>0.1573805179116896</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.278093362574747</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4479302342675445</v>
+        <v>0.1573805019695007</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4479302502097334</v>
+        <v>0.1573805179116896</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.278093362574747</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4479302342675445</v>
+        <v>0.1573805019695007</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4479302900652057</v>
+        <v>0.1573805577671619</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4479302900652057</v>
+        <v>0.1573805577671619</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.6780933625747476</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4479302900652057</v>
+        <v>0.1573805577671619</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4479304415160003</v>
+        <v>0.1573807092179565</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.278093362574747</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4479306567355508</v>
+        <v>0.1573809244375071</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4479305690535118</v>
+        <v>0.157380836755468</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.278093362574747</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4479305212269451</v>
+        <v>0.1573807889289013</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4479305690535118</v>
+        <v>0.157380836755468</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4479303857183391</v>
+        <v>0.1573806534202953</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4479303936894336</v>
+        <v>0.1573806613913898</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.6780933625747476</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4479304016605281</v>
+        <v>0.1573806693624842</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4479304096316225</v>
+        <v>0.1573806773335787</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.278093362574747</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4479304096316225</v>
+        <v>0.1573806773335787</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.278093362574747</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4479304494870948</v>
+        <v>0.157380717189051</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.278093362574747</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4479305132558506</v>
+        <v>0.1573807809578069</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.278093362574747</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.447930624851173</v>
+        <v>0.1573808925531292</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.703898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4479306726777398</v>
+        <v>0.157380940379696</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.278093362574747</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4479306328222675</v>
+        <v>0.1573809005242237</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.6780933625747476</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4479305610824174</v>
+        <v>0.1573808287843736</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4479306806488342</v>
+        <v>0.1573809483507904</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.6780933625747476</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4479305212269451</v>
+        <v>0.1573807889289013</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4479302900652057</v>
+        <v>0.1573805577671619</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4479302422386389</v>
+        <v>0.1573805099405951</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4479302741230167</v>
+        <v>0.157380541824973</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.6780933625747476</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4479303378917724</v>
+        <v>0.1573806055937286</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4479303378917724</v>
+        <v>0.1573806055937286</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4479302581808278</v>
+        <v>0.157380525882784</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4479301386144108</v>
+        <v>0.157380406316367</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.278093362574747</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4479300987589385</v>
+        <v>0.1573803664608947</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.278093362574747</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4479302422386389</v>
+        <v>0.1573805099405951</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.703898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4479303777472446</v>
+        <v>0.1573806454492009</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.703898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4479303618050557</v>
+        <v>0.157380629507012</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4479303378917724</v>
+        <v>0.1573806055937286</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4479302980363001</v>
+        <v>0.1573805657382563</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4479301944120722</v>
+        <v>0.1573804621140284</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.278093362574747</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4479300748456551</v>
+        <v>0.1573803425476113</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.703898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4479301944120722</v>
+        <v>0.1573804621140284</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.278093362574747</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4479302422386389</v>
+        <v>0.1573805099405951</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.703898596494605</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4479303378917724</v>
+        <v>0.1573806055937286</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.278093362574747</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4479302183253556</v>
+        <v>0.1573804860273118</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.278093362574747</v>
+        <v>-1.155749764472209</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.44793022629645</v>
+        <v>0.1573804939984062</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_3_000001.xlsx
+++ b/out/Attention-Mamba1_repeat_3_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.278093362574747</v>
+        <v>0.830692591479827</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.278093362574747</v>
+        <v>0.830692591479827</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.278093362574747</v>
+        <v>0.830692591479827</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.278093362574747</v>
+        <v>0.830692591479827</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.278093362574747</v>
+        <v>0.830692591479827</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.278093362574747</v>
+        <v>0.830692591479827</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.278093362574747</v>
+        <v>0.830692591479827</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0001553836047814693</v>
+        <v>-0.0001515121202140581</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.06690366882491081</v>
+        <v>0.06523671997456126</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.133985885853162</v>
+        <v>0.130647539506708</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2584842548940672</v>
+        <v>0.2520439499138313</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.5842218166266187</v>
+        <v>0.5696655463550505</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.07951069678184169</v>
+        <v>0.07752962286742786</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.4844327552037521</v>
+        <v>0.4723627949662281</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.01613351839373679</v>
+        <v>0.01573154375998933</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4370636886960296</v>
+        <v>0.4261739523065032</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01397234394911369</v>
+        <v>0.01362385826319653</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.4488570223789166</v>
+        <v>0.4376734501270975</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.006829273075512044</v>
+        <v>0.006659168767681518</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.4485266902939701</v>
+        <v>0.4373512155220897</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.003256345633814244</v>
+        <v>0.003175496868870273</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.4482035681335223</v>
+        <v>0.4370360107046152</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001353929605622277</v>
+        <v>0.001319970283236796</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.4476506684643822</v>
+        <v>0.4364968029157771</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0009364392178318687</v>
+        <v>0.0009132890731310851</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.4481691592863425</v>
+        <v>0.4370022110853407</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0003880150844352673</v>
+        <v>0.0003783507790803017</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.6780933625747476</v>
+        <v>0.6306925914798269</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.4480075992920722</v>
+        <v>0.4368446253283382</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.000198792341387696</v>
+        <v>0.0001934469684988384</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.6780933625747476</v>
+        <v>-0.05090557059316809</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.4480167832095169</v>
+        <v>0.4368534378358377</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>7.530420522688556e-05</v>
+        <v>7.320474888108464e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-2.303898596494605</v>
+        <v>-0.05090557059316805</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.4479676905145862</v>
+        <v>0.4368054978911011</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>3.852012786152756e-05</v>
+        <v>3.737486133885577e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.6780933625747476</v>
+        <v>-0.732503732666163</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.4479699102782724</v>
+        <v>0.4368075289196</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>1.645752582315463e-05</v>
+        <v>1.589285409096635e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-2.303898596494605</v>
+        <v>-0.732503732666163</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.4479642480169663</v>
+        <v>0.4368018838764576</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.414101894739158</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.447957981009678</v>
+        <v>0.4367956487535469</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-3.882814673064221e-07</v>
+        <v>-8.494533205757797e-07</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.414101894739158</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.4479515346964202</v>
+        <v>0.4367892753317647</v>
       </c>
     </row>
     <row r="60">
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.414101894739158</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4479460509595846</v>
+        <v>0.4367837915949291</v>
       </c>
     </row>
     <row r="61">
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.414101894739158</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.4479405707350173</v>
+        <v>0.4367783113703618</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-2.303898596494605</v>
+        <v>-0.7325037326661632</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4479351633923603</v>
+        <v>0.4367729040277049</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.278093362574747</v>
+        <v>-0.7325037326661632</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4479302422386389</v>
+        <v>0.4367679828739834</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.703898596494605</v>
+        <v>0.1490944294068319</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4479302820941112</v>
+        <v>0.4367680227294558</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.278093362574747</v>
+        <v>-0.5325037326661631</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4479302741230167</v>
+        <v>0.4367680147583612</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.703898596494605</v>
+        <v>0.1490944294068319</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4479304335449059</v>
+        <v>0.4367681741802504</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.278093362574747</v>
+        <v>0.1490944294068319</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4479303378917724</v>
+        <v>0.4367680785271169</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.278093362574747</v>
+        <v>0.149094429406832</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4479306886199287</v>
+        <v>0.4367684292552732</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.703898596494605</v>
+        <v>0.149094429406832</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4479304415160003</v>
+        <v>0.4367681821513448</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.278093362574747</v>
+        <v>-0.5325037326661631</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4479304016605281</v>
+        <v>0.4367681422958726</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-2.303898596494605</v>
+        <v>-0.7325037326661632</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4479303378917724</v>
+        <v>0.4367680785271169</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-2.303898596494605</v>
+        <v>-0.7325037326661632</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4479304096316225</v>
+        <v>0.436768150266967</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.6780933625747476</v>
+        <v>-0.05090557059316816</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4479303378917724</v>
+        <v>0.4367680785271169</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.278093362574747</v>
+        <v>0.830692591479827</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4479304415160003</v>
+        <v>0.4367681821513448</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.278093362574747</v>
+        <v>0.1490944294068318</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.447930537169134</v>
+        <v>0.4367682778044785</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.703898596494605</v>
+        <v>-0.5325037326661631</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4479304734003781</v>
+        <v>0.4367682140357226</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-2.303898596494605</v>
+        <v>-0.7325037326661632</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4479304335449059</v>
+        <v>0.4367681741802504</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.6780933625747476</v>
+        <v>-0.7325037326661632</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4479304096316225</v>
+        <v>0.436768150266967</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-2.303898596494605</v>
+        <v>-0.7325037326661632</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4479301625276944</v>
+        <v>0.4367679031630389</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-2.303898596494605</v>
+        <v>-0.7325037326661632</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4479300828167496</v>
+        <v>0.4367678234520941</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.6780933625747476</v>
+        <v>-0.7325037326661632</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4479301306433163</v>
+        <v>0.4367678712786608</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-2.303898596494605</v>
+        <v>-0.05090557059316826</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4479302502097334</v>
+        <v>0.4367679908450779</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.278093362574747</v>
+        <v>-0.7325037326661632</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4479302342675445</v>
+        <v>0.436767974902889</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-2.303898596494605</v>
+        <v>0.1490944294068318</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4479302502097334</v>
+        <v>0.4367679908450779</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.278093362574747</v>
+        <v>-0.5325037326661631</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4479302342675445</v>
+        <v>0.436767974902889</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-2.303898596494605</v>
+        <v>-0.5325037326661631</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4479302900652057</v>
+        <v>0.4367680307005502</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-2.303898596494605</v>
+        <v>-0.7325037326661632</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4479302900652057</v>
+        <v>0.4367680307005502</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.6780933625747476</v>
+        <v>-0.7325037326661632</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4479302900652057</v>
+        <v>0.4367680307005502</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-2.303898596494605</v>
+        <v>0.1490944294068318</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4479304415160003</v>
+        <v>0.4367681821513448</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.278093362574747</v>
+        <v>-0.5325037326661631</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4479306567355508</v>
+        <v>0.4367683973708953</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-2.303898596494605</v>
+        <v>0.1490944294068318</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4479305690535118</v>
+        <v>0.4367683096888564</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.278093362574747</v>
+        <v>-0.5325037326661631</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4479305212269451</v>
+        <v>0.4367682618622896</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-2.303898596494605</v>
+        <v>-0.5325037326661631</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4479305690535118</v>
+        <v>0.4367683096888564</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.414101894739158</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4479303857183391</v>
+        <v>0.4367681263536837</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-2.303898596494605</v>
+        <v>-0.7325037326661632</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4479303936894336</v>
+        <v>0.4367681343247781</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.6780933625747476</v>
+        <v>-0.7325037326661632</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4479304016605281</v>
+        <v>0.4367681422958726</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-2.303898596494605</v>
+        <v>0.1490944294068318</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4479304096316225</v>
+        <v>0.436768150266967</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.278093362574747</v>
+        <v>0.1490944294068318</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4479304096316225</v>
+        <v>0.436768150266967</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.278093362574747</v>
+        <v>0.830692591479827</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4479304494870948</v>
+        <v>0.4367681901224393</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.278093362574747</v>
+        <v>0.830692591479827</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4479305132558506</v>
+        <v>0.4367682538911952</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.278093362574747</v>
+        <v>0.1490944294068318</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.447930624851173</v>
+        <v>0.4367683654865175</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.703898596494605</v>
+        <v>0.1490944294068318</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4479306726777398</v>
+        <v>0.4367684133130843</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.278093362574747</v>
+        <v>0.1490944294068318</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4479306328222675</v>
+        <v>0.436768373457612</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.6780933625747476</v>
+        <v>-0.05090557059316823</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4479305610824174</v>
+        <v>0.4367683017177619</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-2.303898596494605</v>
+        <v>-0.05090557059316823</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4479306806488342</v>
+        <v>0.4367684212841788</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.6780933625747476</v>
+        <v>-0.7325037326661632</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4479305212269451</v>
+        <v>0.4367682618622896</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-2.303898596494605</v>
+        <v>-0.7325037326661632</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4479302900652057</v>
+        <v>0.4367680307005502</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.414101894739158</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4479302422386389</v>
+        <v>0.4367679828739834</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-2.303898596494605</v>
+        <v>-0.7325037326661632</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4479302741230167</v>
+        <v>0.4367680147583612</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.6780933625747476</v>
+        <v>-0.7325037326661632</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4479303378917724</v>
+        <v>0.4367680785271169</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-2.303898596494605</v>
+        <v>-0.7325037326661632</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4479303378917724</v>
+        <v>0.4367680785271169</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.414101894739158</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4479302581808278</v>
+        <v>0.4367679988161723</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-2.303898596494605</v>
+        <v>-0.7325037326661632</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4479301386144108</v>
+        <v>0.4367678792497553</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.278093362574747</v>
+        <v>-0.0509055705931683</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4479300987589385</v>
+        <v>0.436767839394283</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.278093362574747</v>
+        <v>0.1490944294068317</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4479302422386389</v>
+        <v>0.4367679828739834</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.703898596494605</v>
+        <v>-0.5325037326661631</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4479303777472446</v>
+        <v>0.4367681183825892</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.703898596494605</v>
+        <v>-1.214101894739158</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4479303618050557</v>
+        <v>0.4367681024404003</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.414101894739158</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4479303378917724</v>
+        <v>0.4367680785271169</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-2.303898596494605</v>
+        <v>-1.414101894739158</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4479302980363001</v>
+        <v>0.4367680386716447</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-2.303898596494605</v>
+        <v>-0.7325037326661632</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4479301944120722</v>
+        <v>0.4367679350474167</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.278093362574747</v>
+        <v>-0.7325037326661632</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4479300748456551</v>
+        <v>0.4367678154809996</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.703898596494605</v>
+        <v>0.1490944294068318</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4479301944120722</v>
+        <v>0.4367679350474167</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.278093362574747</v>
+        <v>-0.5325037326661631</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4479302422386389</v>
+        <v>0.4367679828739834</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.703898596494605</v>
+        <v>0.1490944294068318</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4479303378917724</v>
+        <v>0.4367680785271169</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.278093362574747</v>
+        <v>0.1490944294068318</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4479302183253556</v>
+        <v>0.4367679589607001</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.278093362574747</v>
+        <v>0.830692591479827</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.44793022629645</v>
+        <v>0.4367679669317945</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_3_000001.xlsx
+++ b/out/Attention-Mamba1_repeat_3_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.000111456960439682</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.6306925914798269</v>
+        <v>-0.72</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.002081241458654404</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.6306925914798269</v>
+        <v>-0.7899999999999999</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.0004300996661186218</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.830692591479827</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.0005348846316337585</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.830692591479827</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.001062911003828049</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.830692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.0007332116365432739</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.830692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.0006508342921733856</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.830692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.00170338898897171</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.830692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.001841925084590912</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.830692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.001500725746154785</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.6306925914798269</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.001374572515487671</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.6306925914798269</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.001626752316951752</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.6306925914798269</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.002462998032569885</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.6306925914798269</v>
+        <v>0.16</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.00235309824347496</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.6306925914798269</v>
+        <v>0.3</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.002398431301116943</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.6306925914798269</v>
+        <v>0.3</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.00141771137714386</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.6306925914798269</v>
+        <v>0.3</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>2.804026007652283e-05</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.6306925914798269</v>
+        <v>0.16</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.0009133368730545044</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.6306925914798269</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.0007973648607730865</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.6306925914798269</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.0002627633512020111</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.6306925914798269</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.000398881733417511</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.6306925914798269</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.0004157349467277527</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.6306925914798269</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.0001628734171390533</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.6306925914798269</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.001031115651130676</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.6306925914798269</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.0001767836511135101</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.6306925914798269</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.0004771947860717773</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.6306925914798269</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.0005461424589157104</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.6306925914798269</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.001178231090307236</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.6306925914798269</v>
+        <v>0.16</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.001640923321247101</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.6306925914798269</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.0009752959012985229</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.6306925914798269</v>
+        <v>0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.0003870278596878052</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.6306925914798269</v>
+        <v>0.16</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.0001159049570560455</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.6306925914798269</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.001307692378759384</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.6306925914798269</v>
+        <v>0.16</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.001512631773948669</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.6306925914798269</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.002022426575422287</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.6306925914798269</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.001943372189998627</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.6306925914798269</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.001937136054039001</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.6306925914798269</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.002350151538848877</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.6306925914798269</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.004375476390123367</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.6306925914798269</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.004885483533143997</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.6306925914798269</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.01495471224188805</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.6306925914798269</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.02196142822504044</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.6306925914798269</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0001515121202140581</v>
+        <v>-0.0001816752822221024</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.06523671997456126</v>
+        <v>0.07822410178061202</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.05804530531167984</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.6306925914798269</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.130647539506708</v>
+        <v>0.1566569630070983</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2520439499138313</v>
+        <v>0.3022210742498265</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.06954099237918854</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.6306925914798269</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.5696655463550505</v>
+        <v>0.6830750487817598</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.07752962286742786</v>
+        <v>0.09296489660347235</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.01438858732581139</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.6306925914798269</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.4723627949662281</v>
+        <v>0.5664011813620098</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.01573154375998933</v>
+        <v>0.01886306248949166</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.01824377477169037</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.6306925914798269</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4261739523065032</v>
+        <v>0.5110173888417329</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01362385826319653</v>
+        <v>0.01633660823303623</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.0003317296504974365</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.6306925914798269</v>
+        <v>-0.3</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.4376734501270975</v>
+        <v>0.5248062758631562</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.006659168767681518</v>
+        <v>0.007985702361668543</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.007887978106737137</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.6306925914798269</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.4373512155220897</v>
+        <v>0.524420894243811</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.003175496868870273</v>
+        <v>0.003808255384588791</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.002281717956066132</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.6306925914798269</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.4370360107046152</v>
+        <v>0.5240439424238605</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001319970283236796</v>
+        <v>0.001583850919478074</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.002850309014320374</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.6306925914798269</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.4364968029157771</v>
+        <v>0.5233983419913631</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0009132890731310851</v>
+        <v>0.001096175216267276</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.0009645372629165649</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.6306925914798269</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.4370022110853407</v>
+        <v>0.5240054028804111</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0003783507790803017</v>
+        <v>0.0004543766478726977</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.008826445788145065</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.6306925914798269</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.4368446253283382</v>
+        <v>0.5238174288811471</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0001934469684988384</v>
+        <v>0.0002335372651652704</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.006051946431398392</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.05090557059316809</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.4368534378358377</v>
+        <v>0.5238290030499527</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>7.320474888108464e-05</v>
+        <v>8.842580738814138e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.00139404833316803</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.05090557059316805</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.4368054978911011</v>
+        <v>0.5237725621866074</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>3.737486133885577e-05</v>
+        <v>4.596436025889411e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.0004562102258205414</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.732503732666163</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.4368075289196</v>
+        <v>0.5237760087290115</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>1.589285409096635e-05</v>
+        <v>2.041022794847258e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.001833673566579819</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.732503732666163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.4368018838764576</v>
+        <v>0.5237702339116556</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>5.123686696358992e-06</v>
+        <v>6.722163543152517e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.0003093220293521881</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.414101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.4367956487535469</v>
+        <v>0.5237637718849604</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-8.494533205757797e-07</v>
+        <v>7.289038596293463e-08</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.0006700977683067322</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.414101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.4367892753317647</v>
+        <v>0.5237571092005268</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-2.932986608081494e-06</v>
+        <v>-2.519583929697793e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.0004707314074039459</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.414101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4367837915949291</v>
+        <v>0.5237515287163241</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.36427134277522e-06</v>
+        <v>-4.04640701416283e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.0005560368299484253</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.414101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.4367783113703618</v>
+        <v>0.5237459518591734</v>
       </c>
     </row>
     <row r="62">
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.0002224892377853394</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.7325037326661632</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4367729040277049</v>
+        <v>0.5237405445165164</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.001176226884126663</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.7325037326661632</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4367679828739834</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.0008141882717609406</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.1490944294068319</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4367680227294558</v>
+        <v>0.5237356632182673</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.002576269209384918</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.5325037326661631</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4367680147583612</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.0002168789505958557</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.1490944294068319</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4367681741802504</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.006669454276561737</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.1490944294068319</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4367680785271169</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>5.434080958366394e-05</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.149094429406832</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4367684292552732</v>
+        <v>0.5237360697440847</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.0009549595415592194</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.149094429406832</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4367681821513448</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.001315288245677948</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.5325037326661631</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4367681422958726</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.0008582286536693573</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7325037326661632</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4367680785271169</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.0003321580588817596</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7325037326661632</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.436768150266967</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.0009664818644523621</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.05090557059316816</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4367680785271169</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.02427151426672935</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.830692591479827</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4367681821513448</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.0004760771989822388</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.1490944294068318</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4367682778044785</v>
+        <v>0.52373591829329</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.00239875540137291</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.5325037326661631</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4367682140357226</v>
+        <v>0.5237358545245342</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.0009687915444374084</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7325037326661632</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4367681741802504</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.0001503452658653259</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7325037326661632</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.436768150266967</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.001767106354236603</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7325037326661632</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4367679031630389</v>
+        <v>0.5237355436518504</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.0003981068730354309</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.7325037326661632</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4367678234520941</v>
+        <v>0.5237354639409056</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.0001817569136619568</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7325037326661632</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4367678712786608</v>
+        <v>0.5237355117674724</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.0006758049130439758</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.05090557059316826</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4367679908450779</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.0001429133117198944</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.7325037326661632</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.436767974902889</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.0005097053945064545</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.1490944294068318</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4367679908450779</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.0002903491258621216</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5325037326661631</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.436767974902889</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.0006743445992469788</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5325037326661631</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4367680307005502</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.0003343038260936737</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.7325037326661632</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4367680307005502</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.003424476832151413</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.7325037326661632</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4367680307005502</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.0007056370377540588</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.1490944294068318</v>
+        <v>0.16</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4367681821513448</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.00480242446064949</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.5325037326661631</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4367683973708953</v>
+        <v>0.5237360378597069</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.002474740147590637</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.1490944294068318</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4367683096888564</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.0004847943782806396</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.5325037326661631</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4367682618622896</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.000816740095615387</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5325037326661631</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4367683096888564</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.001054465770721436</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.414101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4367681263536837</v>
+        <v>0.5237357668424952</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.0002781115472316742</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.7325037326661632</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4367681343247781</v>
+        <v>0.5237357748135897</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.0004693120718002319</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.7325037326661632</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4367681422958726</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.0008790232241153717</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.1490944294068318</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.436768150266967</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.0004460066556930542</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.1490944294068318</v>
+        <v>0.16</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.436768150266967</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.002909623086452484</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.830692591479827</v>
+        <v>0.3</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4367681901224393</v>
+        <v>0.5237358306112508</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.0004127174615859985</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.830692591479827</v>
+        <v>0.3</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4367682538911952</v>
+        <v>0.5237358943800067</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.0009133145213127136</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.1490944294068318</v>
+        <v>0.16</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4367683654865175</v>
+        <v>0.5237360059753291</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.001096758991479874</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.1490944294068318</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4367684133130843</v>
+        <v>0.5237360538018958</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.0003626011312007904</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.1490944294068318</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.436768373457612</v>
+        <v>0.5237360139464236</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.001189596951007843</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.05090557059316823</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4367683017177619</v>
+        <v>0.5237359422065735</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.0002367570996284485</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.05090557059316823</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4367684212841788</v>
+        <v>0.5237360617729903</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.0002882368862628937</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7325037326661632</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4367682618622896</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.001390330493450165</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7325037326661632</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4367680307005502</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.0001728720963001251</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.414101894739158</v>
+        <v>0.16</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4367679828739834</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.0001657269895076752</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7325037326661632</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4367680147583612</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.0001540780067443848</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.7325037326661632</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4367680785271169</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.001179978251457214</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7325037326661632</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4367680785271169</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.0005645379424095154</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.414101894739158</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4367679988161723</v>
+        <v>0.5237356393049839</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.0006191767752170563</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.7325037326661632</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4367678792497553</v>
+        <v>0.5237355197385668</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.0006803944706916809</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.0509055705931683</v>
+        <v>0.3</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.436767839394283</v>
+        <v>0.5237354798830945</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.0007173717021942139</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.1490944294068317</v>
+        <v>0.3</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4367679828739834</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.0002672784030437469</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5325037326661631</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4367681183825892</v>
+        <v>0.5237357588714008</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.0008186511695384979</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.214101894739158</v>
+        <v>0.16</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4367681024404003</v>
+        <v>0.5237357429292118</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.0002177208662033081</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.414101894739158</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4367680785271169</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.000456392765045166</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.414101894739158</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4367680386716447</v>
+        <v>0.5237356791604562</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.0002996474504470825</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7325037326661632</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4367679350474167</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.001604590564966202</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7325037326661632</v>
+        <v>0.3</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4367678154809996</v>
+        <v>0.5237354559698112</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.0007319450378417969</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.1490944294068318</v>
+        <v>0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4367679350474167</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.0008004046976566315</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.5325037326661631</v>
+        <v>0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4367679828739834</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.001100491732358932</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.1490944294068318</v>
+        <v>0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4367680785271169</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.0001608915627002716</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.1490944294068318</v>
+        <v>0.2300000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4367679589607001</v>
+        <v>0.5237355994495116</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.000554349273443222</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.830692591479827</v>
+        <v>0.3</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4367679669317945</v>
+        <v>0.5237356074206061</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_3_000001.xlsx
+++ b/out/Attention-Mamba1_repeat_3_000001.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.000111456960439682</v>
+        <v>0.0001114755868911743</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.72</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.002081241458654404</v>
+        <v>0.002081256359815598</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.7899999999999999</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.0004300996661186218</v>
+        <v>0.0004300922155380249</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.8599999999999999</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.0005348846316337585</v>
+        <v>0.000534839928150177</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.8599999999999999</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.0007332116365432739</v>
+        <v>0.0007331930100917816</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.0006508342921733856</v>
+        <v>0.0006508305668830872</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.00170338898897171</v>
+        <v>0.001703411340713501</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.001374572515487671</v>
+        <v>0.001374561339616776</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.8599999999999999</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.001626752316951752</v>
+        <v>0.001626759767532349</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.1199999999999999</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.002462998032569885</v>
+        <v>0.002463031560182571</v>
       </c>
       <c r="JB14" t="n">
         <v>0.16</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.00235309824347496</v>
+        <v>0.002353090792894363</v>
       </c>
       <c r="JB15" t="n">
         <v>0.3</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.002398431301116943</v>
+        <v>0.002398405224084854</v>
       </c>
       <c r="JB16" t="n">
         <v>0.3</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.00141771137714386</v>
+        <v>0.001417718827724457</v>
       </c>
       <c r="JB17" t="n">
         <v>0.3</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>2.804026007652283e-05</v>
+        <v>2.802163362503052e-05</v>
       </c>
       <c r="JB18" t="n">
         <v>0.16</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.0009133368730545044</v>
+        <v>0.0009133629500865936</v>
       </c>
       <c r="JB19" t="n">
         <v>-0.1199999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.0007973648607730865</v>
+        <v>0.0007973462343215942</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.8599999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.0002627633512020111</v>
+        <v>0.0002627409994602203</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.8599999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.000398881733417511</v>
+        <v>0.0003988929092884064</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.9999999999999998</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.0004157349467277527</v>
+        <v>0.0004157163202762604</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.8599999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.0001628734171390533</v>
+        <v>0.0001628771424293518</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.8599999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.001031115651130676</v>
+        <v>0.001031111925840378</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.8599999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.0001767836511135101</v>
+        <v>0.000176798552274704</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.8599999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.0004771947860717773</v>
+        <v>0.0004771724343299866</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.7199999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.0005461424589157104</v>
+        <v>0.0005461163818836212</v>
       </c>
       <c r="JB28" t="n">
         <v>0.02000000000000007</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.001178231090307236</v>
+        <v>0.001178249716758728</v>
       </c>
       <c r="JB29" t="n">
         <v>0.16</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.001640923321247101</v>
+        <v>0.001640908420085907</v>
       </c>
       <c r="JB30" t="n">
         <v>0.1600000000000001</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.0009752959012985229</v>
+        <v>0.0009752772748470306</v>
       </c>
       <c r="JB31" t="n">
         <v>0.16</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.0003870278596878052</v>
+        <v>0.0003869794309139252</v>
       </c>
       <c r="JB32" t="n">
         <v>0.16</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.0001159049570560455</v>
+        <v>0.0001158975064754486</v>
       </c>
       <c r="JB33" t="n">
         <v>0.02000000000000007</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.001512631773948669</v>
+        <v>0.001512665301561356</v>
       </c>
       <c r="JB35" t="n">
         <v>0.4399999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.002022426575422287</v>
+        <v>0.002022441476583481</v>
       </c>
       <c r="JB36" t="n">
         <v>0.7199999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.001943372189998627</v>
+        <v>0.001943368464708328</v>
       </c>
       <c r="JB37" t="n">
         <v>0.8599999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.001937136054039001</v>
+        <v>0.001937165856361389</v>
       </c>
       <c r="JB38" t="n">
         <v>0.9999999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.002350151538848877</v>
+        <v>0.002350132912397385</v>
       </c>
       <c r="JB39" t="n">
         <v>0.9999999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.004375476390123367</v>
+        <v>0.004375465214252472</v>
       </c>
       <c r="JB40" t="n">
         <v>0.9999999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.004885483533143997</v>
+        <v>0.004885490983724594</v>
       </c>
       <c r="JB41" t="n">
         <v>0.9999999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.01495471224188805</v>
+        <v>0.01495472714304924</v>
       </c>
       <c r="JB42" t="n">
         <v>0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.05804530531167984</v>
+        <v>0.05804532021284103</v>
       </c>
       <c r="JB44" t="n">
         <v>0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.06954099237918854</v>
+        <v>0.06954091787338257</v>
       </c>
       <c r="JB45" t="n">
         <v>0.9999999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.01438858732581139</v>
+        <v>0.01438858360052109</v>
       </c>
       <c r="JB46" t="n">
         <v>0.1199999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.01824377477169037</v>
+        <v>0.01824380457401276</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.02000000000000007</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.0003317296504974365</v>
+        <v>0.0003317259252071381</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.3</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.007887978106737137</v>
+        <v>0.007888004183769226</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.5799999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.002281717956066132</v>
+        <v>0.002281706780195236</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.8599999999999999</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.002850309014320374</v>
+        <v>0.002850305289030075</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.5799999999999998</v>
@@ -42281,10 +42281,10 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.0009645372629165649</v>
+        <v>0.0009645484387874603</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC52" t="n">
         <v>0.5240054028804111</v>
@@ -43076,10 +43076,10 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.008826445788145065</v>
+        <v>0.008826479315757751</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC53" t="n">
         <v>0.5238174288811471</v>
@@ -43871,10 +43871,10 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.006051946431398392</v>
+        <v>0.006051972508430481</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC54" t="n">
         <v>0.5238290030499527</v>
@@ -44666,10 +44666,10 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.00139404833316803</v>
+        <v>-0.001394052058458328</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC55" t="n">
         <v>0.5237725621866074</v>
@@ -45461,10 +45461,10 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.0004562102258205414</v>
+        <v>0.0004561804234981537</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
         <v>0.5237760087290115</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.0003093220293521881</v>
+        <v>-0.000309288501739502</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.0006700977683067322</v>
+        <v>-0.0006700828671455383</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.0004707314074039459</v>
+        <v>-0.0004707090556621552</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.9999999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.0005560368299484253</v>
+        <v>-0.0005560293793678284</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.0002224892377853394</v>
+        <v>-0.0002225078642368317</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.001176226884126663</v>
+        <v>0.001176238059997559</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.0008141882717609406</v>
+        <v>-0.0008141770958900452</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.002576269209384918</v>
+        <v>0.002576258033514023</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
         <v>0.5237356552471728</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.0002168789505958557</v>
+        <v>-0.0002168603241443634</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
         <v>0.5237358146690619</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.006669454276561737</v>
+        <v>0.006669435650110245</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
         <v>0.5237357190159284</v>
@@ -55001,10 +55001,10 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>5.434080958366394e-05</v>
+        <v>5.43445348739624e-05</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
         <v>0.5237360697440847</v>
@@ -55796,10 +55796,10 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.0009549595415592194</v>
+        <v>-0.0009549744427204132</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
         <v>0.5237358226401564</v>
@@ -56591,10 +56591,10 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.001315288245677948</v>
+        <v>0.001315280795097351</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3999999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
         <v>0.5237357827846841</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.0008582286536693573</v>
+        <v>-0.0008582212030887604</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,10 +58181,10 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.0003321580588817596</v>
+        <v>-0.000332176685333252</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC72" t="n">
         <v>0.5237357907557786</v>
@@ -58976,10 +58976,10 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.0009664818644523621</v>
+        <v>0.0009664781391620636</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC73" t="n">
         <v>0.5237357190159284</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.02427151426672935</v>
+        <v>0.02427150681614876</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.1199999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.0004760771989822388</v>
+        <v>0.000476054847240448</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.1199999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.00239875540137291</v>
+        <v>-0.002398721873760223</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.1199999999999999</v>
@@ -62159,7 +62159,7 @@
         <v>-0.0009687915444374084</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9999999999999998</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC77" t="n">
         <v>0.5237358146690619</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.0001503452658653259</v>
+        <v>0.0001503638923168182</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.001767106354236603</v>
+        <v>-0.001767110079526901</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.9999999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.0003981068730354309</v>
+        <v>-0.0003981217741966248</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.9999999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.0001817569136619568</v>
+        <v>0.0001817457377910614</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.9999999999999998</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.0006758049130439758</v>
+        <v>-0.0006758086383342743</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.9999999999999998</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.0005097053945064545</v>
+        <v>-0.0005097277462482452</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.9999999999999998</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.0002903491258621216</v>
+        <v>0.0002903379499912262</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.9999999999999998</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.0006743445992469788</v>
+        <v>-0.0006743334233760834</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.1199999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.0003343038260936737</v>
+        <v>-0.0003343075513839722</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.1199999999999999</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.0007056370377540588</v>
+        <v>-0.0007056333124637604</v>
       </c>
       <c r="JB89" t="n">
         <v>0.16</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.00480242446064949</v>
+        <v>0.004802446812391281</v>
       </c>
       <c r="JB90" t="n">
         <v>0.1600000000000001</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.002474740147590637</v>
+        <v>-0.002474792301654816</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.1199999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.0004847943782806396</v>
+        <v>0.0004847906529903412</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.1199999999999999</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.001054465770721436</v>
+        <v>-0.001054488122463226</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.9999999999999998</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.0004693120718002319</v>
+        <v>0.0004693306982517242</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.8599999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.0008790232241153717</v>
+        <v>-0.000879041850566864</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.5799999999999998</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.0004460066556930542</v>
+        <v>0.0004460327327251434</v>
       </c>
       <c r="JB98" t="n">
         <v>0.16</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.002909623086452484</v>
+        <v>0.002909637987613678</v>
       </c>
       <c r="JB99" t="n">
         <v>0.3</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.0004127174615859985</v>
+        <v>0.0004127249121665955</v>
       </c>
       <c r="JB100" t="n">
         <v>0.3</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.001096758991479874</v>
+        <v>-0.001096762716770172</v>
       </c>
       <c r="JB102" t="n">
         <v>0.02000000000000007</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.0003626011312007904</v>
+        <v>0.0003625974059104919</v>
       </c>
       <c r="JB103" t="n">
         <v>0.02000000000000007</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.001189596951007843</v>
+        <v>0.001189611852169037</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.5799999999999998</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.0002367570996284485</v>
+        <v>-0.0002367608249187469</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.5799999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.0002882368862628937</v>
+        <v>0.0002882145345211029</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.4399999999999999</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.001390330493450165</v>
+        <v>-0.00139034166932106</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.4399999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.0001728720963001251</v>
+        <v>-0.0001728758215904236</v>
       </c>
       <c r="JB108" t="n">
         <v>0.16</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.0001657269895076752</v>
+        <v>-0.0001657344400882721</v>
       </c>
       <c r="JB109" t="n">
         <v>0.02000000000000007</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.0001540780067443848</v>
+        <v>0.0001541003584861755</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.5799999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.001179978251457214</v>
+        <v>-0.001179981976747513</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.7199999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.0005645379424095154</v>
+        <v>-0.0005645193159580231</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.5799999999999998</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.0006191767752170563</v>
+        <v>-0.0006191879510879517</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.4399999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.0006803944706916809</v>
+        <v>0.000680387020111084</v>
       </c>
       <c r="JB114" t="n">
         <v>0.3</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.0007173717021942139</v>
+        <v>0.0007173977792263031</v>
       </c>
       <c r="JB115" t="n">
         <v>0.3</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.0002672784030437469</v>
+        <v>-0.0002672746777534485</v>
       </c>
       <c r="JB116" t="n">
         <v>0.4399999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.0008186511695384979</v>
+        <v>-0.0008186623454093933</v>
       </c>
       <c r="JB117" t="n">
         <v>0.16</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.0002177208662033081</v>
+        <v>-0.000217728316783905</v>
       </c>
       <c r="JB118" t="n">
         <v>0.02000000000000007</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.000456392765045166</v>
+        <v>-0.0004563741385936737</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.4399999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.0002996474504470825</v>
+        <v>-0.0002996325492858887</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.4399999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.001604590564966202</v>
+        <v>0.001604598015546799</v>
       </c>
       <c r="JB121" t="n">
         <v>0.3</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.0007319450378417969</v>
+        <v>-0.0007319115102291107</v>
       </c>
       <c r="JB122" t="n">
         <v>0.3</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.0008004046976566315</v>
+        <v>0.0008003786206245422</v>
       </c>
       <c r="JB123" t="n">
         <v>0.3</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.001100491732358932</v>
+        <v>-0.001100514084100723</v>
       </c>
       <c r="JB124" t="n">
         <v>0.16</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.0001608915627002716</v>
+        <v>0.0001608692109584808</v>
       </c>
       <c r="JB125" t="n">
         <v>0.2300000000000001</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.000554349273443222</v>
+        <v>0.0005543716251850128</v>
       </c>
       <c r="JB126" t="n">
         <v>0.3</v>
